--- a/data/ai_active/구성종목_2026-06-09.xlsx
+++ b/data/ai_active/구성종목_2026-06-09.xlsx
@@ -140,7 +140,7 @@
     <t>38,038,957</t>
   </si>
   <si>
-    <t>NQM6 Index</t>
+    <t>NQM6 INDEX</t>
   </si>
   <si>
     <t>NASDAQ 100 E-MINI INDEX JUN 2026</t>
